--- a/output/exports/VN_Index_Quant_Model_Complete_Architecture_Values.xlsx
+++ b/output/exports/VN_Index_Quant_Model_Complete_Architecture_Values.xlsx
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>33.97</v>
+        <v>31.5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="7"/>
@@ -828,13 +828,13 @@
         <v>0.25</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>57.92</v>
+        <v>58.47</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>8.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.0614426826</v>
+        <v>0.06292784630000001</v>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>0.2</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>36.4</v>
+        <v>32.9</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.058020751</v>
+        <v>0.0592532275</v>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         <v>0.2</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>40.39</v>
+        <v>41.08</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.0316338564</v>
+        <v>0.0302390502</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -900,13 +900,13 @@
         <v>0.15</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>50.84</v>
+        <v>51.6</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>6.04</v>
+        <v>5.57</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.0459299261</v>
+        <v>0.0426408885</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         <v>0.1</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>41.57</v>
+        <v>39.52</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.3624966185</v>
+        <v>0.3573566744</v>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
@@ -948,13 +948,13 @@
         <v>0.1</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>60.43</v>
+        <v>55.67</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>57.924675</v>
+        <v>58.4657958451</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.4404761656</v>
+        <v>0.447582313</v>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>47.664</v>
+        <v>46.6725</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>131.504675</v>
+        <v>130.6257958451</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>0.0573663669</v>
+        <v>0.0570334713</v>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>0.07697146169999999</v>
+        <v>0.07700542539999999</v>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>0.1606617136</v>
+        <v>0.156267837</v>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.192687747</v>
+        <v>0.2114624506</v>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>0.4782608696</v>
+        <v>0.5217391304</v>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>ema_20</t>
+          <t>m2_yoy_pct</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.02178040146827698</v>
+        <v>0.01707467995584011</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>0.0217804015</v>
+        <v>0.01707468</v>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>macd_line</t>
+          <t>bb_lower</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0.02076428011059761</v>
+        <v>0.01457174587994814</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>0.0425446816</v>
+        <v>0.0316464258</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>etf_flow_q_zscore</t>
+          <t>ema_20</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Flow / Structure</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D8" s="34" t="n">
-        <v>0.01783575303852558</v>
+        <v>0.01421605050563812</v>
       </c>
       <c r="E8" s="35" t="n">
-        <v>0.0603804346</v>
+        <v>0.0458624763</v>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0.01772940717637539</v>
+        <v>0.0133400084450841</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>0.0781098418</v>
+        <v>0.0592024848</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D10" s="34" t="n">
-        <v>0.01733604446053505</v>
+        <v>0.01314797159284353</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>0.0954458863</v>
+        <v>0.0723504564</v>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>usd_vnd_zscore_lag1</t>
+          <t>us10y_zscore_1y</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.0167862419039011</v>
+        <v>0.01264037005603313</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>0.1122321282</v>
+        <v>0.0849908264</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -1371,19 +1371,19 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>us10y_zscore_1y</t>
+          <t>oil_n_shock_days_ytd</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Global / Rates</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D12" s="34" t="n">
-        <v>0.01557330787181854</v>
+        <v>0.01242248620837927</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>0.127805436</v>
+        <v>0.0974133126</v>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>oil_n_shock_days_ytd</t>
+          <t>macd_line</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0.01539521757513285</v>
+        <v>0.01232288777828217</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>0.1432006536</v>
+        <v>0.1097362004</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -1423,19 +1423,19 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>etf_flow_q_zscore_live</t>
+          <t>oil_max_weekly_change_ytd</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Flow / Structure</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D14" s="34" t="n">
-        <v>0.01488733943551779</v>
+        <v>0.01212919689714909</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>0.158087993</v>
+        <v>0.1218653973</v>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
@@ -1449,19 +1449,19 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>dxy_zscore_60d</t>
+          <t>valuation_composite_score</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Global / Rates</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0.01360253803431988</v>
+        <v>0.01088140346109867</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>0.1716905311</v>
+        <v>0.1327468008</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>bb_lower</t>
+          <t>headline_pe</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.0134799899533391</v>
+        <v>0.01080580707639456</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>0.185170521</v>
+        <v>0.1435526079</v>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
@@ -1501,19 +1501,19 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>ex_vingroup_pe</t>
+          <t>dxy_zscore_60d</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Technical / Market</t>
+          <t>Global / Rates</t>
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.01324111688882113</v>
+        <v>0.01069003902375698</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>0.1984116379</v>
+        <v>0.1542426469</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>nff_ex_etf_q_ytd</t>
+          <t>nff_ex_etf_rolling60d</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="D18" s="34" t="n">
-        <v>0.01247525215148926</v>
+        <v>0.01060809195041656</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>0.2108868901</v>
+        <v>0.1648507388</v>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>nff_ex_etf_rolling60d</t>
+          <t>price_vs_ma200</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0.01242704410105944</v>
+        <v>0.01058133877813816</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>0.2233139342</v>
+        <v>0.1754320776</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>rvol_10d</t>
+          <t>macd_signal</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="D20" s="34" t="n">
-        <v>0.01225554849952459</v>
+        <v>0.01048300601541996</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>0.2355694827</v>
+        <v>0.1859150836</v>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>22</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" s="30" t="n">
         <v>125.7537097965</v>
@@ -3087,7 +3087,7 @@
         <v>0.1107919426</v>
       </c>
       <c r="E26" s="35" t="n">
-        <v>-0.0426503083</v>
+        <v>-0.0491341444</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>0.008686168899999999</v>
       </c>
       <c r="J26" s="35" t="n">
-        <v>0.0035525212</v>
+        <v>0.0029041376</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>135.5249381036</v>
+        <v>135.4373770174</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>149.456120325</v>
+        <v>148.4438998187</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>135.5249381036</v>
+        <v>135.4373770174</v>
       </c>
       <c r="N26" s="35" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>156.1144497415</v>
       </c>
       <c r="S26" s="35" t="n">
-        <v>-0.0426503083</v>
+        <v>-0.0491341444</v>
       </c>
     </row>
     <row r="27">
@@ -3144,13 +3144,13 @@
         <v>1860.01</v>
       </c>
       <c r="C27" s="30" t="n">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="D27" s="35" t="n">
-        <v>-0.0426503083</v>
+        <v>-0.0491341444</v>
       </c>
       <c r="E27" s="35" t="n">
-        <v>0</v>
+        <v>-0.0109237711</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -3167,34 +3167,34 @@
         <v>0.009179820999999999</v>
       </c>
       <c r="J27" s="35" t="n">
-        <v>0.0082618389</v>
+        <v>0.0071694618</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>136.6446233066</v>
+        <v>136.4083901147</v>
       </c>
       <c r="L27" s="30" t="n">
-        <v>149.456120325</v>
+        <v>146.8223326395</v>
       </c>
       <c r="M27" s="30" t="n">
-        <v>136.6446233066</v>
+        <v>136.4083901147</v>
       </c>
       <c r="N27" s="35" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R27" s="30" t="n">
         <v>156.1144497415</v>
       </c>
       <c r="S27" s="35" t="n">
-        <v>-0.0426503083</v>
+        <v>-0.0595211854</v>
       </c>
     </row>
     <row r="28">
@@ -3204,12 +3204,14 @@
         </is>
       </c>
       <c r="B28" s="37" t="n">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="C28" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="35" t="inlineStr"/>
+        <v>1749.3</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>-0.0109237711</v>
+      </c>
       <c r="E28" s="35" t="n">
         <v>0</v>
       </c>
@@ -3225,19 +3227,19 @@
         <v>0.9</v>
       </c>
       <c r="I28" s="35" t="n">
-        <v>0.009517025300000001</v>
+        <v>0.009427071299999999</v>
       </c>
       <c r="J28" s="35" t="n">
-        <v>0.0085653228</v>
+        <v>0.0084843642</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>137.81502861</v>
+        <v>137.5657285697</v>
       </c>
       <c r="L28" s="30" t="n">
-        <v>149.456120325</v>
+        <v>146.8223326395</v>
       </c>
       <c r="M28" s="30" t="n">
-        <v>137.81502861</v>
+        <v>137.5657285697</v>
       </c>
       <c r="N28" s="35" t="n">
         <v>0</v>
@@ -3251,7 +3253,7 @@
         <v>156.1144497415</v>
       </c>
       <c r="S28" s="35" t="n">
-        <v>-0.0426503083</v>
+        <v>-0.0595211854</v>
       </c>
     </row>
     <row r="29"/>
@@ -3296,13 +3298,13 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>0.3781502861</v>
+        <v>0.3756572857</v>
       </c>
       <c r="C32" s="35" t="n">
-        <v>0.4945612032</v>
+        <v>0.4682233264</v>
       </c>
       <c r="D32" s="35" t="n">
-        <v>-0.1164109171</v>
+        <v>-0.0925660407</v>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
@@ -3317,13 +3319,13 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>0.0573663669</v>
+        <v>0.0570334713</v>
       </c>
       <c r="C33" s="35" t="n">
-        <v>0.072383713</v>
+        <v>0.06907291090000001</v>
       </c>
       <c r="D33" s="35" t="n">
-        <v>-0.0150173461</v>
+        <v>-0.0120394396</v>
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
@@ -3359,13 +3361,13 @@
         </is>
       </c>
       <c r="B35" s="14" t="n">
-        <v>0.07697146169999999</v>
+        <v>0.07700542539999999</v>
       </c>
       <c r="C35" s="35" t="n">
-        <v>0.1862738965</v>
+        <v>0.186984213</v>
       </c>
       <c r="D35" s="35" t="n">
-        <v>-0.1093024348</v>
+        <v>-0.1099787876</v>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
@@ -3380,13 +3382,13 @@
         </is>
       </c>
       <c r="B36" s="17" t="n">
-        <v>0.1606617136</v>
+        <v>0.156267837</v>
       </c>
       <c r="C36" s="31" t="n">
-        <v>0.1470077855</v>
+        <v>0.1287430126</v>
       </c>
       <c r="D36" s="31" t="n">
-        <v>0.013653928</v>
+        <v>0.0275248243</v>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
@@ -3401,13 +3403,13 @@
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>0.192687747</v>
+        <v>0.2114624506</v>
       </c>
       <c r="C37" s="31" t="n">
-        <v>0.2246096607</v>
+        <v>0.2279927511</v>
       </c>
       <c r="D37" s="31" t="n">
-        <v>-0.0319219136</v>
+        <v>-0.0165303005</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -3422,7 +3424,7 @@
         </is>
       </c>
       <c r="B38" s="14" t="n">
-        <v>0.4782608696</v>
+        <v>0.5217391304</v>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
@@ -3798,7 +3800,7 @@
         </is>
       </c>
       <c r="B7" s="40" t="n">
-        <v>33.97</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="8">
@@ -3820,7 +3822,7 @@
         </is>
       </c>
       <c r="B9" s="40" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="10"/>
@@ -4105,7 +4107,7 @@
         </is>
       </c>
       <c r="B7" s="40" t="n">
-        <v>33.97</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="8">
@@ -4127,7 +4129,7 @@
         </is>
       </c>
       <c r="B9" s="40" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="10"/>
@@ -5030,28 +5032,28 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7040,7 +7042,7 @@
         <v>1860.01</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>3.7228</v>
@@ -7117,64 +7119,66 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>1780.68</v>
-      </c>
-      <c r="D28" s="25" t="n"/>
+        <v>1768.62</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>1749.3</v>
+      </c>
       <c r="E28" s="26" t="n">
-        <v>3.8615</v>
+        <v>3.824486217282372</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>0.004357</v>
+        <v>-0.006669987027570823</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>4.4753</v>
+        <v>4.490338434500489</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>0.5289</v>
+        <v>0.5641762386393379</v>
       </c>
       <c r="I28" s="26" t="n">
-        <v>-1.27</v>
+        <v>-1.2883999557269</v>
       </c>
       <c r="J28" s="26" t="n">
         <v>14.98</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>1.05</v>
+        <v>1.561003392211543</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>5.18</v>
+        <v>5.293000221252441</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>-0.0525</v>
+        <v>-0.1220948548235693</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>-0.1609</v>
+        <v>-0.1801222314895506</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>-0.16</v>
+        <v>-0.5758618955754176</v>
       </c>
       <c r="P28" s="26" t="n">
-        <v>43.8</v>
+        <v>43.81259366342714</v>
       </c>
       <c r="Q28" s="26" t="n">
-        <v>0.8055707548717673</v>
+        <v>0.7509441191245513</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>0.6810894520369312</v>
+        <v>0.638044654231649</v>
       </c>
       <c r="S28" s="26" t="n">
-        <v>20</v>
+        <v>20.39884195572824</v>
       </c>
       <c r="T28" s="26" t="n">
-        <v>-1.250996235356308</v>
+        <v>-1.222708307670604</v>
       </c>
       <c r="U28" s="26" t="n"/>
       <c r="V28" s="27" t="n">
-        <v>-0.119329</v>
+        <v>-0.1226154130605057</v>
       </c>
       <c r="W28" s="15" t="inlineStr">
         <is>
@@ -7182,13 +7186,13 @@
         </is>
       </c>
       <c r="X28" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y28" s="26" t="n">
-        <v>-0.1187</v>
+        <v>-0.1147552691905312</v>
       </c>
       <c r="Z28" s="27" t="n">
-        <v>0.0011</v>
+        <v>0.001304077894212551</v>
       </c>
     </row>
   </sheetData>
@@ -9098,71 +9102,71 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>59.939</v>
+        <v>60.457192958</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>49.5643</v>
+        <v>50.6669987028</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>69.05</v>
+        <v>69.32599933589999</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>68.08</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>42.990075</v>
+        <v>43.7987882289</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>29</v>
+        <v>18.7799321558</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>49.2125</v>
+        <v>48.1685771776</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>47.6</v>
+        <v>41.3620715664</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>56.2</v>
+        <v>56.1874063366</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>29.8607311282</v>
+        <v>31.2263970219</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>32.9727636991</v>
+        <v>34.0488836442</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>80</v>
+        <v>79.60115804430001</v>
       </c>
       <c r="P28" s="10" t="n">
-        <v>18.7250941161</v>
+        <v>19.4322923082</v>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>38</v>
+        <v>45.2596836337</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>55.5</v>
+        <v>50.7329131136</v>
       </c>
       <c r="S28" s="10" t="n">
-        <v>39.71</v>
+        <v>45.86</v>
       </c>
       <c r="T28" s="10" t="n">
-        <v>42.3605</v>
+        <v>36.8075</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>38.0671</v>
+        <v>37.7384586939</v>
       </c>
       <c r="W28" s="10" t="n">
-        <v>48.2195</v>
+        <v>48.2786709621</v>
       </c>
     </row>
   </sheetData>
@@ -10921,65 +10925,65 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>57.92</v>
+        <v>58.47</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>36.4</v>
+        <v>32.9</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>40.39</v>
+        <v>41.08</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>50.84</v>
+        <v>51.6</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>41.57</v>
+        <v>39.52</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>60.43</v>
+        <v>55.67</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>7.28</v>
+        <v>6.58</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>8.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>6.04</v>
+        <v>5.57</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
       <c r="P28" s="29" t="n">
-        <v>57.924675</v>
+        <v>58.4657958451</v>
       </c>
       <c r="Q28" s="29" t="n">
-        <v>36.4025</v>
+        <v>32.8995974473</v>
       </c>
       <c r="R28" s="29" t="n">
-        <v>40.3896472358</v>
+        <v>41.0771827547</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>50.842</v>
+        <v>51.5983688536</v>
       </c>
       <c r="T28" s="29" t="n">
-        <v>41.56535</v>
+        <v>39.52325</v>
       </c>
       <c r="U28" s="29" t="n">
-        <v>60.4288666667</v>
+        <v>55.672376552</v>
       </c>
     </row>
   </sheetData>
@@ -12778,14 +12782,14 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -12802,10 +12806,10 @@
         <v>6.0119786553</v>
       </c>
       <c r="I28" s="31" t="n">
-        <v>-1.0689528536</v>
+        <v>-1.2336240969</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>33.97</v>
+        <v>31.5</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -12818,14 +12822,14 @@
         </is>
       </c>
       <c r="M28" s="10" t="n">
-        <v>9.949999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>24.03</v>
+        <v>25.57</v>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
@@ -12840,7 +12844,7 @@
         <v>60.061</v>
       </c>
       <c r="S28" s="12" t="n">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
     </row>
   </sheetData>
@@ -12863,8 +12867,8 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -13624,26 +13628,26 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="15" t="n">
         <v>2130</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.1342</v>
+        <v>0.08520704799252052</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.1092</v>
+        <v>0.06020704799252052</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002370158183153296</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>1.092</v>
+        <v>0.6020704799</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>38</v>
+        <v>45.2596836337</v>
       </c>
     </row>
   </sheetData>
@@ -13671,7 +13675,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -14570,35 +14574,35 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.0072</v>
+        <v>0</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.4775</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>0.5699</v>
+        <v>0.3701</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>0.6359</v>
+        <v>0.725</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>0.9498</v>
+        <v>0.7961</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="33" t="n">
-        <v>0.0011</v>
+        <v>0.0001465826227169615</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>55.5</v>
+        <v>50.7329131136</v>
       </c>
     </row>
   </sheetData>
@@ -15774,7 +15778,7 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -15786,13 +15790,13 @@
         <v>8</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>0.425</v>
+        <v>0.4846</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>0.3692</v>
+        <v>0.4326</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-1</v>
@@ -15803,13 +15807,13 @@
         </is>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.5031</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>39.71</v>
+        <v>45.86</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>42.3605</v>
+        <v>36.8075</v>
       </c>
     </row>
   </sheetData>
